--- a/Result/profitability/3303.xlsx
+++ b/Result/profitability/3303.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.045</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>35.96875</v>
+        <v>35.8725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8550000000000001</v>
+        <v>0.925</v>
       </c>
       <c r="N3" t="n">
-        <v>33.91125</v>
+        <v>34.13625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>0.925</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>32.08625</v>
+        <v>31.85375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8462500000000002</v>
+        <v>0.9387500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>29.57125</v>
+        <v>29.20125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7900000000000001</v>
+        <v>0.77625</v>
       </c>
       <c r="N6" t="n">
-        <v>27.1575</v>
+        <v>27.78</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.56125</v>
+        <v>0.61625</v>
       </c>
       <c r="N7" t="n">
-        <v>25.7</v>
+        <v>26.2325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5062500000000001</v>
+        <v>0.5762499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>24.79625</v>
+        <v>25.34125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.38</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4387500000000001</v>
+        <v>0.43875</v>
       </c>
       <c r="N9" t="n">
         <v>22.79875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>979</v>
+      </c>
+      <c r="D75" t="n">
+        <v>601</v>
+      </c>
+      <c r="E75" t="n">
+        <v>378</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>199</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>200</v>
+      </c>
+      <c r="K75" t="n">
+        <v>138</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.15625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>37.42375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6086956521739129</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.127150772820064</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.960000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07113674597452535</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
